--- a/Employee_Reports_wi48/Mark Merill Jovenes Tirol Q0506.xlsx
+++ b/Employee_Reports_wi48/Mark Merill Jovenes Tirol Q0506.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -789,53 +789,53 @@
       <c r="K7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Weight scales (Cargo Trainings)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>LSME-CRG-M-013</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>12-Aug-2024</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>12-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>09-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>08-Apr-2028</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>632</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,68 +1019,68 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Truck dock (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-006</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
           <t>12-Jul-2026</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Truck dock (Cargo Trainings)</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>LSME-CRG-M-006</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>EQUIPMENT MANUAL</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>21-Aug-2024</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>21-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>11-Jul-2028</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>726</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Control circuits (Cargo Trainings)</t>
+          <t>Truck dock 20FT (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-019</t>
+          <t>LSME-CRG-M-020</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1108,20 +1108,20 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>19-Feb-2026</t>
+          <t>12-Jul-2026</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>19-Feb-2028</t>
+          <t>11-Jul-2028</t>
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>586</v>
+        <v>726</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Cool Room (Cargo Trainings)</t>
+          <t>Control circuits (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-011</t>
+          <t>LSME-CRG-M-019</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1157,20 +1157,20 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>29-Sep-2024</t>
+          <t>19-Feb-2026</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>19-Feb-2028</t>
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>78</v>
+        <v>583</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Climate Control Center (Cargo Trainings)</t>
+          <t>Cool Room (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-014</t>
+          <t>LSME-CRG-M-011</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1206,20 +1206,20 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>20-Jan-2025</t>
+          <t>29-Sep-2024</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>20-Jan-2027</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>191</v>
+        <v>75</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>3TIER RACK -G/H/A/303 (Cargo Trainings)</t>
+          <t>Climate Control Center (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-015</t>
+          <t>LSME-CRG-M-014</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1255,20 +1255,20 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>19-Jan-2025</t>
+          <t>20-Jan-2025</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>19-Jan-2027</t>
+          <t>20-Jan-2027</t>
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>3TIER RACK -JBAY (Cargo Trainings)</t>
+          <t>3TIER RACK -G/H/A/303 (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-017</t>
+          <t>LSME-CRG-M-015</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Non-powered roller Decks (Cargo Trainings)</t>
+          <t>3TIER RACK -JBAY (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-016</t>
+          <t>LSME-CRG-M-017</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1382,28 +1382,40 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Powered roller Decks2 (Cargo Trainings)</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
+          <t>Non-powered roller Decks (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-016</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>19-Jan-2025</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>18-Feb-2028</t>
+          <t>19-Jan-2027</t>
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>585</v>
+        <v>187</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1419,146 +1431,134 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
+          <t>Powered roller Decks2 (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>18-Feb-2026</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>18-Feb-2028</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>582</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
           <t>Lodige LOTO Procedure (SOPs)</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>ELECTRICAL SAFETY</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>LSME-OHS-SOP-021</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>05-Nov-2025</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>05-Nov-2026</t>
         </is>
       </c>
-      <c r="H21" s="3" t="n">
-        <v>115</v>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="H22" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Equipment  Request &amp;handover procedure(SOP-028) (SOPs)</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-028</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>12-Jul-2025</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>12-Jul-2026</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Equipment  Request &amp;handover procedure(SOP-028) (SOPs)</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>LSME-CRG-SOP-028</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>12-Jul-2025</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="H23" s="5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>STACKER CRANE AISLE MONTHLY PREVENTIVE MAINTENANCE (SOPs)</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>LSME-CRG-SOP-035</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>05-Nov-2025</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>05-Nov-2026</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>115</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -1566,183 +1566,183 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
+          <t>STACKER CRANE AISLE MONTHLY PREVENTIVE MAINTENANCE (SOPs)</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-035</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>05-Nov-2025</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>05-Nov-2026</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
           <t>Endangered by Electricity A safety Training (SOPs)</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>09-Nov-2025</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>09-Nov-2026</t>
         </is>
       </c>
-      <c r="H24" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="H25" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Incident Escalation Process(LSME-IMS-SOP-021 ) (SOPs)</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>IMS</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>LSME-IMS-SOP-021</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>22-Mar-2025</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>22-Mar-2026</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n">
-        <v>-113</v>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="H26" s="5" t="n">
+        <v>-116</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="K26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Misaligned Pallet-ULD Recovery Procedure (SOPs)</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-030</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>14-Jan-2026</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>14-Jan-2027</t>
         </is>
       </c>
-      <c r="H26" s="3" t="n">
-        <v>185</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Contigency Plan During Heavy Rainfall (SOPs)</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>IMS</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>LSME-IMS-SOP-018</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>09-Apr-2025</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>09-Apr-2026</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>-95</v>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRED</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr"/>
+      <c r="H27" s="3" t="n">
+        <v>182</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -1750,134 +1750,146 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
+          <t>Contigency Plan During Heavy Rainfall (SOPs)</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-018</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>09-Apr-2025</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>09-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-98</v>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>29-May-2025</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>29-May-2026</t>
         </is>
       </c>
-      <c r="H28" s="5" t="n">
-        <v>-45</v>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="H29" s="5" t="n">
+        <v>-48</v>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Replacement Procedure Of ASI Gateway (SOPs)</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-041</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>23-Apr-2026</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>23-Apr-2027</t>
         </is>
       </c>
-      <c r="H29" s="3" t="n">
-        <v>284</v>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Stacker Crane Aisle Annual Maintenance And Megger Test Procedure (SOPs)</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>LSME-CRG-SOP-003</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>25-Jul-2025</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>25-Jul-2026</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr"/>
+      <c r="H30" s="3" t="n">
+        <v>281</v>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -1885,17 +1897,17 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Weight Scale Verification Procedure(LSME-IMS-SOP-023 ) (SOPs)</t>
+          <t>Stacker Crane Aisle Annual Maintenance And Megger Test Procedure (SOPs)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>IMS</t>
+          <t>CARGO</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>LSME-IMS-SOP-023</t>
+          <t>LSME-CRG-SOP-003</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1905,20 +1917,20 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>18-Jul-2025</t>
+          <t>25-Jul-2025</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>18-Jul-2026</t>
+          <t>25-Jul-2026</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -1934,17 +1946,17 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Replacement of Stacker Crane Driven Wheel (SOPs)</t>
+          <t>Weight Scale Verification Procedure(LSME-IMS-SOP-023 ) (SOPs)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>CARGO</t>
+          <t>IMS</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-009</t>
+          <t>LSME-IMS-SOP-023</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -1954,20 +1966,20 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>25-Jul-2025</t>
+          <t>18-Jul-2025</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>25-Jul-2026</t>
+          <t>18-Jul-2026</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -1983,7 +1995,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Replacement of Stacker Crane Fork Flyer Chain (SOPs)</t>
+          <t>Replacement of Stacker Crane Driven Wheel (SOPs)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1993,7 +2005,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-010</t>
+          <t>LSME-CRG-SOP-009</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -2003,20 +2015,20 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>26-Jul-2025</t>
+          <t>25-Jul-2025</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>26-Jul-2026</t>
+          <t>25-Jul-2026</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2032,122 +2044,122 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
+          <t>Replacement of Stacker Crane Fork Flyer Chain (SOPs)</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-010</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>26-Jul-2025</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>26-Jul-2026</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
           <t>Replacement of Stacker Crane Wire Rope (SOPs)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr"/>
-      <c r="D34" s="4" t="inlineStr"/>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>24-Jul-2025</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>24-Jul-2026</t>
         </is>
       </c>
-      <c r="H34" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="H35" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>EXPIRING SOON</t>
         </is>
       </c>
-      <c r="K34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr"/>
+      <c r="D36" s="3" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>30-Sep-2025</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>30-Sep-2026</t>
         </is>
       </c>
-      <c r="H35" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Replacing Bearings Of ULD Hoist Counterweight Pulley (SOPs)</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>LSME-CRG-SOP-011</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>15-Aug-2025</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>15-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr"/>
+      <c r="H36" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -2155,85 +2167,97 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
+          <t>Replacing Bearings Of ULD Hoist Counterweight Pulley (SOPs)</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-011</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>15-Aug-2025</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>15-Aug-2026</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
           <t>Overload and Load Testing Procedure In ULD Hoist (SOPs)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-018</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>15-Aug-2025</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>15-Aug-2026</t>
         </is>
       </c>
-      <c r="H37" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="H38" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>EXPIRING SOON</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>EOP For ULD System Failure (SOPs)</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="3" t="inlineStr"/>
-      <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>25-Oct-2025</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>25-Oct-2026</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>104</v>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
+      <c r="K38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
@@ -2241,7 +2265,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>EOP For CS System Failure (SOPs)</t>
+          <t>EOP For ULD System Failure (SOPs)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr"/>
@@ -2258,11 +2282,11 @@
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2278,7 +2302,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>20FT Floor Scale Weight Discrepancy Troubleshooting Guide (SOPs)</t>
+          <t>EOP For CS System Failure (SOPs)</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr"/>
@@ -2286,20 +2310,20 @@
       <c r="E40" s="3" t="inlineStr"/>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>29-Jan-2026</t>
+          <t>25-Oct-2025</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>29-Jan-2027</t>
+          <t>25-Oct-2026</t>
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>200</v>
+        <v>101</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -2315,7 +2339,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>PM Of CS H9 TV (SOPs)</t>
+          <t>20FT Floor Scale Weight Discrepancy Troubleshooting Guide (SOPs)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr"/>
@@ -2323,20 +2347,20 @@
       <c r="E41" s="3" t="inlineStr"/>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>29-Jan-2026</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>11-Jun-2027</t>
+          <t>29-Jan-2027</t>
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>333</v>
+        <v>197</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -2352,7 +2376,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>IS0 55001 (Other Trainings)</t>
+          <t>PM Of CS H9 TV (SOPs)</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
@@ -2360,28 +2384,65 @@
       <c r="E42" s="3" t="inlineStr"/>
       <c r="F42" s="3" t="inlineStr">
         <is>
+          <t>11-Jun-2026</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>11-Jun-2027</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>330</v>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>IS0 55001 (Other Trainings)</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
           <t>12-Jul-2025</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>12-Jul-2027</t>
         </is>
       </c>
-      <c r="H42" s="3" t="n">
-        <v>364</v>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="n">
+        <v>361</v>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2993,7 +3054,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3022,7 +3083,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7966</v>
+        <v>7963</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3051,7 +3112,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3080,7 +3141,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7949</v>
+        <v>7946</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -3109,7 +3170,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7949</v>
+        <v>7946</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -3138,7 +3199,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7962</v>
+        <v>7959</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -3167,7 +3228,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7956</v>
+        <v>7953</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3196,7 +3257,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7956</v>
+        <v>7953</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -3225,7 +3286,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7959</v>
+        <v>7956</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -3254,7 +3315,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7959</v>
+        <v>7956</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -3283,7 +3344,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7962</v>
+        <v>7959</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -3312,7 +3373,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7962</v>
+        <v>7959</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -3341,7 +3402,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7963</v>
+        <v>7960</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -3370,7 +3431,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7963</v>
+        <v>7960</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -3399,7 +3460,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7948</v>
+        <v>7945</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -3428,7 +3489,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7955</v>
+        <v>7952</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -3457,7 +3518,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7955</v>
+        <v>7952</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -3486,7 +3547,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7966</v>
+        <v>7963</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -3515,7 +3576,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7966</v>
+        <v>7963</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -3544,7 +3605,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7948</v>
+        <v>7945</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -3573,7 +3634,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7953</v>
+        <v>7950</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
